--- a/education_surveys/023_educational_environment_assessment_quiz--education_surveys.xlsx
+++ b/education_surveys/023_educational_environment_assessment_quiz--education_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>safety</t>
+          <t>teaching_quality</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>How safe do you feel in the classroom?</t>
+          <t>How would you rate the teaching quality?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>teacher_quality</t>
+          <t>safety</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>How would you rate your teaching quality?</t>
+          <t>How safe do you feel in the classroom?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -597,11 +597,7 @@
           <t>Overall Satisfaction</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>What is your overall satisfaction with the class?</t>
-        </is>
-      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -639,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>resources</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>How would you rate the availability of technology resources in the classroom?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -657,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>teaching_quality_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>How would you rate the teaching quality in terms of explaining concepts?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -680,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>comments_2</t>
+          <t>overall_satisfaction_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Do you have any comments or suggestions?</t>
+          <t>Overall Satisfaction 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -708,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>teaching_quality_2</t>
+          <t>safety_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>How would you rate the teaching quality?</t>
+          <t>Safety 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -731,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>safety_2</t>
+          <t>feedback</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>How would you rate your safety?</t>
+          <t>How would you rate the teacher's feedback on your performance?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -749,24 +745,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>overall_satisfaction_2</t>
+          <t>resources_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Overall Satisfaction</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>What is your overall satisfaction with the class?</t>
-        </is>
-      </c>
+          <t>How would you rate the availability of resources in the classroom?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -776,336 +768,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>resources</t>
+          <t>overall_satisfaction_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>How would you rate the classroom resources?</t>
+          <t>Overall Satisfaction 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>teaching_quality_3</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>How would you rate the teaching quality?</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>overall_satisfaction_3</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Overall Satisfaction</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>What is your overall satisfaction with the class?</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>classroom_resources_2</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>How would you rate the classroom resources?</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>teaching_quality_4</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>How would you rate the teaching quality?</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>overall_satisfaction_4</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Overall Satisfaction</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>What is your overall satisfaction with the class?</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>resource</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>How would you rate the resources?</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>teaching_quality_5</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>How would you rate the teaching quality?</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>overall_satisfaction_5</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Overall Satisfaction</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>What is your overall satisfaction with the class?</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>classroom_resources_3</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>How would you rate the classroom resources?</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>resource_2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>How would you rate the classroom resources?</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>resource_3</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>How would you rate the resources?</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>resource_4</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>How would you rate the resources?</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>overall_satisfaction_6</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Overall Satisfaction</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>What is your overall satisfaction with the class?</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1122,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C58"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="47" customWidth="1" min="2" max="2"/>
-    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1155,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'verygood':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'veryGood': 'Very Good'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -1172,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'contentprovided':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'contentProvided': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1189,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'verygood':_'very_good'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'veryGood': 'Very Good'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1206,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'noresources':_'no_resources'}</t>
+          <t>limited_resources</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'noResources': 'No Resources'}</t>
+          <t>Limited Resources</t>
         </is>
       </c>
     </row>
@@ -1223,148 +900,148 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'limitedresources':_'limited_resources'}</t>
+          <t>no_resources</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'limitedResources': 'Limited Resources'}</t>
+          <t>No Resources</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>classroom_resources_choices</t>
+          <t>teaching_quality_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'excellentresources':_'excellent_resources'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'excellentResources': 'Excellent Resources'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>safety_choices</t>
+          <t>teaching_quality_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'safe':_'safe'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'safe': 'Safe'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>safety_choices</t>
+          <t>teaching_quality_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'unsafe':_'unsafe'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'unsafe': 'Unsafe'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>safety_choices</t>
+          <t>teaching_quality_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'unsure':_'unsure'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'unsure': 'Unsure'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>teacher_quality_choices</t>
+          <t>safety_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'verygood':_'very_good'}</t>
+          <t>safe</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'veryGood': 'Very Good'}</t>
+          <t>Safe</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>teacher_quality_choices</t>
+          <t>safety_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'good':_'good'}</t>
+          <t>unsafe</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'good': 'Good'}</t>
+          <t>Unsafe</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>teacher_quality_choices</t>
+          <t>safety_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'fair':_'fair'}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'fair': 'Fair'}</t>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>teacher_quality_choices</t>
+          <t>overall_satisfaction_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'poor':_'poor'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'poor': 'Poor'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1053,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'verygood':_'very_good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'veryGood': 'Very Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1393,12 +1070,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'good':_'good'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'good': 'Good'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1410,709 +1087,335 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'fair':_'fair'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'fair': 'Fair'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>overall_satisfaction_choices</t>
+          <t>teaching_quality_1_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'poor':_'poor'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'poor': 'Poor'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>teaching_quality_2_choices</t>
+          <t>teaching_quality_1_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'verygood':_'very_good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'veryGood': 'Very Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>teaching_quality_2_choices</t>
+          <t>teaching_quality_1_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'good':_'good'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'good': 'Good'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>teaching_quality_2_choices</t>
+          <t>teaching_quality_1_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'fair':_'fair'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'fair': 'Fair'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>teaching_quality_2_choices</t>
+          <t>overall_satisfaction_1_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'poor':_'poor'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'poor': 'Poor'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>safety_2_choices</t>
+          <t>overall_satisfaction_1_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'safe':_'safe'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'safe': 'Safe'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>safety_2_choices</t>
+          <t>overall_satisfaction_1_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'unsafe':_'unsafe'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'unsafe': 'Unsafe'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>safety_2_choices</t>
+          <t>overall_satisfaction_1_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'unsure':_'unsure'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'unsure': 'Unsure'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>overall_satisfaction_2_choices</t>
+          <t>safety_1_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'verygood':_'very_good'}</t>
+          <t>safe</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'veryGood': 'Very Good'}</t>
+          <t>Safe</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>overall_satisfaction_2_choices</t>
+          <t>safety_1_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'good':_'good'}</t>
+          <t>unsafe</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'good': 'Good'}</t>
+          <t>Unsafe</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>overall_satisfaction_2_choices</t>
+          <t>safety_1_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'fair':_'fair'}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'fair': 'Fair'}</t>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>overall_satisfaction_2_choices</t>
+          <t>feedback_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'poor':_'poor'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'poor': 'Poor'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>overall_satisfaction_3_choices</t>
+          <t>feedback_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'verygood':_'very_good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'veryGood': 'Very Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>overall_satisfaction_3_choices</t>
+          <t>feedback_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'good':_'good'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'good': 'Good'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>overall_satisfaction_3_choices</t>
+          <t>feedback_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'fair':_'fair'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'fair': 'Fair'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>overall_satisfaction_3_choices</t>
+          <t>overall_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'poor':_'poor'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'poor': 'Poor'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>teaching_quality_4_choices</t>
+          <t>overall_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'verygood':_'very_good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'veryGood': 'Very Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>teaching_quality_4_choices</t>
+          <t>overall_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'good':_'good'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'good': 'Good'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>teaching_quality_4_choices</t>
+          <t>overall_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'fair':_'fair'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'fair': 'Fair'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>teaching_quality_4_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>{'poor':_'poor'}</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>{'poor': 'Poor'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>teaching_quality_5_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>{'verygood':_'very_good'}</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>{'veryGood': 'Very Good'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>teaching_quality_5_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>{'good':_'good'}</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>{'good': 'Good'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>teaching_quality_5_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>{'fair':_'fair'}</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>{'fair': 'Fair'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>overall_satisfaction_5_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>{'verygood':_'very_good'}</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>{'veryGood': 'Very Good'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>overall_satisfaction_5_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>{'good':_'good'}</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>{'good': 'Good'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>overall_satisfaction_5_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>{'fair':_'fair'}</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>{'fair': 'Fair'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>overall_satisfaction_5_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>{'poor':_'poor'}</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>{'poor': 'Poor'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>resource_2_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>{'verygood':_'very_good'}</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>{'veryGood': 'Very Good'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>resource_2_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>{'fair':_'fair'}</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>{'fair': 'Fair'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>resource_2_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>{'limitedresources':_'limited_resources'}</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>{'limitedResources': 'Limited Resources'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>resource_2_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>{'noresources':_'no_resources'}</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>{'noResources': 'No Resources'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>resource_3_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>{'verygood':_'very_good'}</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>{'veryGood': 'Very Good'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>resource_3_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>{'good':_'good'}</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>{'good': 'Good'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>resource_3_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>{'fair':_'fair'}</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>{'fair': 'Fair'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>resource_3_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>{'limitedresources':_'limited_resources'}</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>{'limitedResources': 'Limited Resources'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>resource_4_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>{'verygood':_'very_good'}</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>{'veryGood': 'Very Good'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>resource_4_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>{'good':_'good'}</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>{'good': 'Good'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>overall_satisfaction_6_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>{'verygood':_'very_good'}</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>{'veryGood': 'Very Good'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>overall_satisfaction_6_choices</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>{'good':_'good'}</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>{'good': 'Good'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>overall_satisfaction_6_choices</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>{'fair':_'fair'}</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>{'fair': 'Fair'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>overall_satisfaction_6_choices</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>{'poor':_'poor'}</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>{'poor': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
